--- a/public/crawlability-experis-september-2026.xlsx
+++ b/public/crawlability-experis-september-2026.xlsx
@@ -700,7 +700,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>להריץ מחדש את ה-Website Audit של experis ב-SE Ranking (הסריקה האחרונה: 2024-04-09).</t>
+          <t>להריץ מחדש את ה-Website Audit של experis ב-SE Ranking (הסריקה האחרונה: 2024-04-09); הפעלה מחדש דרך ה-API אינה זמינה בחשבון, יש להפעיל בממשק.</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>להריץ מחדש את ה-Website Audit של experis-academy ב-SE Ranking (הסריקה האחרונה: 2025-02-09).</t>
+          <t>להריץ מחדש את ה-Website Audit של experis-academy ב-SE Ranking (הסריקה האחרונה: 2025-02-09); הפעלה מחדש דרך ה-API אינה זמינה בחשבון, יש להפעיל בממשק.</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>להריץ מחדש את ה-Website Audit של experis-cyber ב-SE Ranking (הסריקה האחרונה: 2025-02-09).</t>
+          <t>להריץ מחדש את ה-Website Audit של experis-cyber ב-SE Ranking (הסריקה האחרונה: 2025-02-09); הפעלה מחדש דרך ה-API אינה זמינה בחשבון, יש להפעיל בממשק.</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>לתקן או להסיר את הקישור בעמודי המקור; להגדיר הפניית 301 ליעד המצוין. באתר קיימים שני עמודים זהים בכותרת (penetrationnew ו-penetration-1testing); להפנות לאחד מהם ולאחד את השני אליו.</t>
+          <t>לתקן או להסיר את הקישור בעמודי המקור. להגדיר הפניית 301 ליעד המצוין (אומת כעמוד תקין ב-27.09.2026). באתר קיימים שני עמודים זהים בכותרת (penetrationnew ו-penetration-1testing); להפנות לאחד מהם ולאחד את השני אליו.</t>
         </is>
       </c>
       <c r="J2" s="6" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>לתקן או להסיר את הקישור בעמודי המקור. לא נמצא עמוד חלופי מובהק; אם קיים, להגדיר הפניית 301 (יעד לאישור). מזהה קורס שנמחק. להסיר את הקישור.</t>
+          <t>מזהה קורס שנמחק. להסיר את הקישור.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
@@ -934,7 +934,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>לתקן או להסיר את הקישור בעמודי המקור.</t>
+          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה; המקור עשוי להיות תגית canonical/hreflang, קובץ סטטי או קישור חיצוני. לאתר את המקור ולתקן; אין צורך בהפניה.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>

--- a/public/crawlability-experis-september-2026.xlsx
+++ b/public/crawlability-experis-september-2026.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -505,7 +505,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>להסיר ממפת האתר כתובת אחת שמחזירה שגיאה, או לתקן את העמוד (במדגם של 294 כתובות שנבדקו; ייתכנו כתובות נוספות).</t>
+          <t>כתובת אחת במפת האתר נמצאת בלולאת הפניות; לתקן את כלל ההפניה ולהסיר מהמפה עד לתיקון.</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>כתובות שבורות (404): 3 כתובות (הבולטת: https://experis.co.il/cyber/penetration-testing/, 2 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים שגויים לתיקון בעמוד המקור (ללא הפניה): כתובת אחת (הבולטת: https://experis.co.il/academy/?post_type=course&amp;p=4118, קישור נכנס אחד). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>הפניות שמובילות לעמוד שגיאה: כתובת אחת (הבולטת: https://experis.co.il/ithitech/אאוטסורסינג/, קישור נכנס אחד). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>כתובות שבורות (404): 2 כתובות (הבולטת: https://experis.co.il/cyber/penetration-testing/, 2 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>לולאות הפניה: כתובת אחת (הבולטת: https://experis.co.il/academy/קורס-תכנות-coding-bootcamps/, קישור נכנס אחד). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>הפניות שמובילות לעמוד שגיאה: כתובת אחת (הבולטת: https://experis.co.il/ithitech/אאוטסורסינג/, קישור נכנס אחד). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
         </is>
       </c>
     </row>
@@ -558,14 +558,14 @@
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>גבוהה</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>להסיר ממפת האתר 1 כתובות עם noindex או canonical לכתובת אחרת.</t>
+          <t>לולאות הפניה: כתובת אחת (הבולטת: https://experis.co.il/academy/קורס-תכנות-coding-bootcamps/, קישור נכנס אחד). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>campaigns.experis.co.il: מארח עותק של אתר הבית לצד עמודי נחיתה (עמוד אחד באינדקס). לוודא ש-canonical מצביע על הדומיין הראשי בכל העמודים, או להגדיר noindex לעותק.</t>
+          <t>להסיר ממפת האתר כתובת אחת עם noindex או canonical לכתובת אחרת.</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>שרשראות הפניות: כתובת אחת (הבולטת: https://experis.co.il/cyber/author/roeed/, 2 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>campaigns.experis.co.il: מארח עותק של אתר הבית לצד עמודי נחיתה (עמוד אחד באינדקס). לוודא ש-canonical מצביע על הדומיין הראשי בכל העמודים, או להגדיר noindex לעותק.</t>
         </is>
       </c>
     </row>
@@ -610,7 +610,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308): כתובת אחת (הבולטת: https://experis.co.il/academy/course/qa-automation-ai/, קישור נכנס אחד). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>שרשראות הפניות: כתובת אחת (הבולטת: https://experis.co.il/cyber/author/roeed/, 2 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים לגרסת דומיין לא קנונית: 2 כתובות (הבולטת: https://www.experis.co.il/cyber/wp-content/uploads/2017/12/mpg_code_business_con, 99 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים פנימיים לגרסת דומיין לא קנונית: 2 כתובות (הבולטת: https://www.experis.co.il/cyber/wp-content/uploads/2017/12/mpg_code_business_con…, 99 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
         </is>
       </c>
     </row>
@@ -633,14 +633,14 @@
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>בינונית</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>להסיר 16 רשומות כפולות ממפת האתר.</t>
+          <t>קישורים פנימיים ללא לוכסן סופי: 6 כתובות (הבולטת: https://experis.co.il/cyber, 97 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>bo.experis.co.il: להגדיר noindex למסכי מערכת.</t>
+          <t>להסיר 16 רשומות כפולות ממפת האתר.</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>jobs.experis.co.il: ה-canonical בעמוד הבית מצביע על כתובת חיפוש בדומיין הראשי (עם &amp;amp; לא מקודד). לוודא canonical תקין.</t>
+          <t>bo.experis.co.il: להגדיר noindex למסכי מערכת.</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים ללא לוכסן סופי: 6 כתובות (הבולטת: https://experis.co.il/cyber, 97 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>jobs.experis.co.il: ה-canonical בעמוד הבית מצביע על כתובת חיפוש בדומיין הראשי (עם &amp;amp; לא מקודד). לוודא canonical תקין.</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>להריץ מחדש את ה-Website Audit של experis ב-SE Ranking (הסריקה האחרונה: 2024-04-09); הפעלה מחדש דרך ה-API אינה זמינה בחשבון, יש להפעיל בממשק.</t>
+          <t>קישורים פנימיים לכתובות שמפנות (301/308): כתובת אחת (הבולטת: https://experis.co.il/academy/course/qa-automation-ai/, קישור נכנס אחד). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>להריץ מחדש את ה-Website Audit של experis-academy ב-SE Ranking (הסריקה האחרונה: 2025-02-09); הפעלה מחדש דרך ה-API אינה זמינה בחשבון, יש להפעיל בממשק.</t>
+          <t>להריץ מחדש את ה-Website Audit של experis ב-SE Ranking (הסריקה האחרונה: 2024-04-09); הפעלה מחדש דרך ה-API אינה זמינה בחשבון, יש להפעיל בממשק.</t>
         </is>
       </c>
     </row>
@@ -729,6 +729,21 @@
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>להריץ מחדש את ה-Website Audit של experis-academy ב-SE Ranking (הסריקה האחרונה: 2025-02-09); הפעלה מחדש דרך ה-API אינה זמינה בחשבון, יש להפעיל בממשק.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>להריץ מחדש את ה-Website Audit של experis-cyber ב-SE Ranking (הסריקה האחרונה: 2025-02-09); הפעלה מחדש דרך ה-API אינה זמינה בחשבון, יש להפעיל בממשק.</t>
         </is>
@@ -745,7 +760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -869,7 +884,7 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>https://experis.co.il/academy/?post_type=course&amp;p=4118</t>
+          <t>https://experis.co.il/ithitech/אאוטסורסינג</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -885,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
@@ -895,97 +910,58 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>מזהה קורס שנמחק. להסיר את הקישור.</t>
+          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה; המקור עשוי להיות תגית canonical/hreflang, קובץ סטטי או קישור חיצוני. לאתר את המקור ולתקן; אין צורך בהפניה.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>גבוהה</t>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
+          <t>https://experis.co.il/ithitech/אאוטסורסינג/</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>308</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>308 -&gt; 404</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
           <t>https://experis.co.il/ithitech/אאוטסורסינג</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>404</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>https://experis.co.il/cyber/סייבר-ושאר-ירקות-סיכום-אירועי-אבטחת/</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>כתובות שבורות (404)</t>
+          <t>הפניות שמובילות לעמוד שגיאה</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה; המקור עשוי להיות תגית canonical/hreflang, קובץ סטטי או קישור חיצוני. לאתר את המקור ולתקן; אין צורך בהפניה.</t>
+          <t>ההפניה מובילה לעמוד שמחזיר 404. להגדיר יעד תקין להפניה או להסיר את הקישור. עמוד 'אאוטסורסינג' (שירותי מיקור חוץ IT) שהוסר; לא נמצא עמוד מקביל בדומיין הראשי. לבחור יעד (עמוד שירותי IT רלוונטי) ולהגדיר 301, או להסיר את הקישור.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>https://experis.co.il/ithitech/אאוטסורסינג/</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>308</v>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>308 -&gt; 404</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>https://experis.co.il/ithitech/אאוטסורסינג</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>https://experis.co.il/cyber/סייבר-ושאר-ירקות-סיכום-אירועי-אבטחת/</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>הפניות שמובילות לעמוד שגיאה</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>ההפניה מובילה לעמוד שמחזיר 404. להגדיר יעד תקין להפניה או להסיר את הקישור. עמוד 'אאוטסורסינג' (שירותי מיקור חוץ IT) שהוסר; לא נמצא עמוד מקביל בדומיין הראשי. לבחור יעד (עמוד שירותי IT רלוונטי) ולהגדיר 301, או להסיר את הקישור.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>גבוהה</t>
         </is>
@@ -2081,7 +2057,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>קישורי Cloudflare (ללא טיפול)</t>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">

--- a/public/crawlability-experis-september-2026.xlsx
+++ b/public/crawlability-experis-september-2026.xlsx
@@ -520,7 +520,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>קישורים שגויים לתיקון בעמוד המקור (ללא הפניה): כתובת אחת (הבולטת: https://experis.co.il/academy/?post_type=course&amp;p=4118, קישור נכנס אחד). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים שגויים לתיקון בעמוד המקור (ללא הפניה): כתובת אחת; הבולטת https://experis.co.il/academy/?post_type=course&amp;p=4118 (קישור נכנס אחד).</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>כתובות שבורות (404): 2 כתובות (הבולטת: https://experis.co.il/cyber/penetration-testing/, 2 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>כתובות שבורות (404): כתובת אחת; הבולטת https://experis.co.il/cyber/penetration-testing/ (2 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>הפניות שמובילות לעמוד שגיאה: כתובת אחת (הבולטת: https://experis.co.il/ithitech/אאוטסורסינג/, קישור נכנס אחד). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>הפניות שמובילות לעמוד שגיאה: כתובת אחת; הבולטת https://experis.co.il/ithitech/אאוטסורסינג/ (קישור נכנס אחד).</t>
         </is>
       </c>
     </row>
@@ -565,7 +565,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>לולאות הפניה: כתובת אחת (הבולטת: https://experis.co.il/academy/קורס-תכנות-coding-bootcamps/, קישור נכנס אחד). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>לולאות הפניה: כתובת אחת; הבולטת https://experis.co.il/academy/קורס-תכנות-coding-bootcamps/ (קישור נכנס אחד).</t>
         </is>
       </c>
     </row>
@@ -610,7 +610,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>שרשראות הפניות: כתובת אחת (הבולטת: https://experis.co.il/cyber/author/roeed/, 2 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>שרשראות הפניות: כתובת אחת; הבולטת https://experis.co.il/cyber/author/roeed/ (2 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים לגרסת דומיין לא קנונית: 2 כתובות (הבולטת: https://www.experis.co.il/cyber/wp-content/uploads/2017/12/mpg_code_business_con…, 99 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים פנימיים לגרסת דומיין לא קנונית: 2 כתובות; הבולטת https://www.experis.co.il/cyber/wp-content/uploads/2017/12/mpg_code_business_con… (99 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים ללא לוכסן סופי: 6 כתובות (הבולטת: https://experis.co.il/cyber, 97 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים פנימיים ללא לוכסן סופי: 6 כתובות; הבולטת https://experis.co.il/cyber (97 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308): כתובת אחת (הבולטת: https://experis.co.il/academy/course/qa-automation-ai/, קישור נכנס אחד). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים פנימיים לכתובות שמפנות (301/308): כתובת אחת; הבולטת https://experis.co.il/academy/course/qa-automation-ai/ (קישור נכנס אחד).</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>להריץ מחדש את ה-Website Audit של experis ב-SE Ranking (הסריקה האחרונה: 2024-04-09); הפעלה מחדש דרך ה-API אינה זמינה בחשבון, יש להפעיל בממשק.</t>
+          <t>להריץ מחדש (בממשק) את ה-Website Audit של experis ב-SE Ranking; הסריקה האחרונה: 2024-04-09.</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>להריץ מחדש את ה-Website Audit של experis-academy ב-SE Ranking (הסריקה האחרונה: 2025-02-09); הפעלה מחדש דרך ה-API אינה זמינה בחשבון, יש להפעיל בממשק.</t>
+          <t>להריץ מחדש (בממשק) את ה-Website Audit של experis-academy ב-SE Ranking; הסריקה האחרונה: 2025-02-09.</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>להריץ מחדש את ה-Website Audit של experis-cyber ב-SE Ranking (הסריקה האחרונה: 2025-02-09); הפעלה מחדש דרך ה-API אינה זמינה בחשבון, יש להפעיל בממשק.</t>
+          <t>להריץ מחדש (בממשק) את ה-Website Audit של experis-cyber ב-SE Ranking; הסריקה האחרונה: 2025-02-09.</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -867,7 +867,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>לתקן או להסיר את הקישור בעמודי המקור. להגדיר הפניית 301 ליעד המצוין (אומת כעמוד תקין ב-27.09.2026). באתר קיימים שני עמודים זהים בכותרת (penetrationnew ו-penetration-1testing); להפנות לאחד מהם ולאחד את השני אליו.</t>
+          <t>לתקן או להסיר את הקישור בעמודי המקור. להגדיר הפניית 301 ליעד המצוין (היעד אומת כעמוד תקין). באתר קיימים שני עמודים זהים בכותרת (penetrationnew ו-penetration-1testing); להפנות לאחד מהם ולאחד את השני אליו.</t>
         </is>
       </c>
       <c r="J2" s="6" t="inlineStr">
@@ -884,84 +884,45 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
+          <t>https://experis.co.il/ithitech/אאוטסורסינג/</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>308</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>308 -&gt; 404</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
           <t>https://experis.co.il/ithitech/אאוטסורסינג</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
-        <v>404</v>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>https://experis.co.il/cyber/סייבר-ושאר-ירקות-סיכום-אירועי-אבטחת/</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>כתובות שבורות (404)</t>
+          <t>הפניות שמובילות לעמוד שגיאה</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה; המקור עשוי להיות תגית canonical/hreflang, קובץ סטטי או קישור חיצוני. לאתר את המקור ולתקן; אין צורך בהפניה.</t>
+          <t>ההפניה מובילה לעמוד שמחזיר 404. להגדיר יעד תקין להפניה או להסיר את הקישור. עמוד 'אאוטסורסינג' (שירותי מיקור חוץ IT) שהוסר; לא נמצא עמוד מקביל בדומיין הראשי. לבחור יעד (עמוד שירותי IT רלוונטי) ולהגדיר 301, או להסיר את הקישור.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>https://experis.co.il/ithitech/אאוטסורסינג/</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>308</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>308 -&gt; 404</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>https://experis.co.il/ithitech/אאוטסורסינג</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>https://experis.co.il/cyber/סייבר-ושאר-ירקות-סיכום-אירועי-אבטחת/</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>הפניות שמובילות לעמוד שגיאה</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>ההפניה מובילה לעמוד שמחזיר 404. להגדיר יעד תקין להפניה או להסיר את הקישור. עמוד 'אאוטסורסינג' (שירותי מיקור חוץ IT) שהוסר; לא נמצא עמוד מקביל בדומיין הראשי. לבחור יעד (עמוד שירותי IT רלוונטי) ולהגדיר 301, או להסיר את הקישור.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>גבוהה</t>
         </is>
@@ -1946,7 +1907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -2022,7 +1983,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>https://experis.co.il/cdn-cgi/l/email-protection</t>
+          <t>https://experis.co.il/ithitech/אאוטסורסינג</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -2038,9 +1999,48 @@
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>כתובות 404 ללא קישור פנימי שאותר</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>לא אותר קישור פנימי לכתובת; לאתר את המקור (canonical, hreflang, קובץ סטטי או קישור חיצוני) ולתקן. אין צורך בהפניה.</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>https://experis.co.il/cdn-cgi/l/email-protection</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>404</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="n">
         <v>437</v>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>https://experis.co.il/
 https://experis.co.il/search?search=DevOps
@@ -2055,18 +2055,18 @@
 (ועוד 40)</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>קישור הגנת דוא"ל של Cloudflare (cdn-cgi). גוגל מתעלם מכתובות cdn-cgi; לא נדרש טיפול. ניתן לבטל את Email Address Obfuscation ב-Cloudflare כדי שהסורקים לא ידווחו על כך.</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>נמוכה</t>
         </is>

--- a/public/crawlability-experis-september-2026.xlsx
+++ b/public/crawlability-experis-september-2026.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -595,7 +595,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>campaigns.experis.co.il: מארח עותק של אתר הבית לצד עמודי נחיתה (עמוד אחד באינדקס). לוודא ש-canonical מצביע על הדומיין הראשי בכל העמודים, או להגדיר noindex לעותק.</t>
+          <t>שרשראות הפניות: כתובת אחת; הבולטת https://experis.co.il/cyber/author/roeed/ (2 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -610,7 +610,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>שרשראות הפניות: כתובת אחת; הבולטת https://experis.co.il/cyber/author/roeed/ (2 קישורים נכנסים).</t>
+          <t>קישורים פנימיים לגרסת דומיין לא קנונית: 2 כתובות; הבולטת https://www.experis.co.il/cyber/wp-content/uploads/2017/12/mpg_code_business_con… (99 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים לגרסת דומיין לא קנונית: 2 כתובות; הבולטת https://www.experis.co.il/cyber/wp-content/uploads/2017/12/mpg_code_business_con… (99 קישורים נכנסים).</t>
+          <t>קישורים פנימיים ללא לוכסן סופי: 6 כתובות; הבולטת https://experis.co.il/cyber (97 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -633,14 +633,14 @@
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים ללא לוכסן סופי: 6 כתובות; הבולטת https://experis.co.il/cyber (97 קישורים נכנסים).</t>
+          <t>bo.experis.co.il: להגדיר noindex למסכי מערכת.</t>
         </is>
       </c>
     </row>
@@ -655,97 +655,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>להסיר 16 רשומות כפולות ממפת האתר.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>bo.experis.co.il: להגדיר noindex למסכי מערכת.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>jobs.experis.co.il: ה-canonical בעמוד הבית מצביע על כתובת חיפוש בדומיין הראשי (עם &amp;amp; לא מקודד). לוודא canonical תקין.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
           <t>קישורים פנימיים לכתובות שמפנות (301/308): כתובת אחת; הבולטת https://experis.co.il/academy/course/qa-automation-ai/ (קישור נכנס אחד).</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>להריץ מחדש (בממשק) את ה-Website Audit של experis ב-SE Ranking; הסריקה האחרונה: 2024-04-09.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>להריץ מחדש (בממשק) את ה-Website Audit של experis-academy ב-SE Ranking; הסריקה האחרונה: 2025-02-09.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>להריץ מחדש (בממשק) את ה-Website Audit של experis-cyber ב-SE Ranking; הסריקה האחרונה: 2025-02-09.</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2854,96 +2764,6 @@
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>campaigns.experis.co.il</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Experis - פתרונות ושירותי IT שדוחפים עסקים קדימה</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>index,follow</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>https://experis.co.il/</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>עותק אתר לקמפיינים (index, follow)</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>מארח עותק של אתר הבית לצד עמודי נחיתה (עמוד אחד באינדקס). לוודא ש-canonical מצביע על הדומיין הראשי בכל העמודים, או להגדיר noindex לעותק.</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>jobs.experis.co.il</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>index,follow</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>https://experis.co.il/search</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>פורטל משרות</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>ה-canonical בעמוד הבית מצביע על כתובת חיפוש בדומיין הראשי (עם &amp;amp; לא מקודד). לוודא canonical תקין.</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>נמוכה</t>
         </is>

--- a/public/crawlability-experis-september-2026.xlsx
+++ b/public/crawlability-experis-september-2026.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -580,7 +580,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>להסיר ממפת האתר כתובת אחת עם noindex או canonical לכתובת אחרת.</t>
+          <t>כתובת אחת במפת האתר עם noindex או canonical לכתובת אחרת (ראו טבלה): לתקן את התגית אם היא שגויה, אחרת להסיר מהמפה.</t>
         </is>
       </c>
     </row>
@@ -656,6 +656,21 @@
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>קישורים פנימיים לכתובות שמפנות (301/308): כתובת אחת; הבולטת https://experis.co.il/academy/course/qa-automation-ai/ (קישור נכנס אחד).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>אחר: 3 כתובות; הבולטת https://experis.co.il/cyber/ (ללא קישורים נכנסים).</t>
         </is>
       </c>
     </row>
